--- a/AT/Research Hours (F26).xlsx
+++ b/AT/Research Hours (F26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abigailtouma/Desktop/SSS-Experiments/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97390012-B5F1-C942-973A-CBFA922F117E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE884E55-4899-3448-AAC2-F0E3A6B644F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="720" windowWidth="27640" windowHeight="16940" xr2:uid="{9D7B63EE-5957-9947-A3B5-024424A2FDD1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -66,6 +66,18 @@
   </si>
   <si>
     <t>same as above</t>
+  </si>
+  <si>
+    <t>continued working on I-Cat examples</t>
+  </si>
+  <si>
+    <t>continued working on I-Cat examples / different carry methods</t>
+  </si>
+  <si>
+    <t>worked on difference method + looked at journals</t>
+  </si>
+  <si>
+    <t>continued to look at journals + worked on a few more examples</t>
   </si>
 </sst>
 </file>
@@ -76,7 +88,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -89,6 +101,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -123,9 +142,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,11 +512,11 @@
       </c>
       <c r="E2" s="3">
         <f>SUM(C2:C48)</f>
-        <v>6.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="8">
+      <c r="A3" s="7">
         <v>46265</v>
       </c>
       <c r="B3" t="s">
@@ -510,7 +527,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
+      <c r="A4" s="7">
         <v>46265</v>
       </c>
       <c r="B4" t="s">
@@ -519,9 +536,10 @@
       <c r="C4">
         <v>1</v>
       </c>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
+      <c r="A5" s="7">
         <v>46268</v>
       </c>
       <c r="B5" t="s">
@@ -532,7 +550,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="8">
+      <c r="A6" s="7">
         <v>46269</v>
       </c>
       <c r="B6" t="s">
@@ -543,7 +561,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="8">
+      <c r="A7" s="7">
         <v>46271</v>
       </c>
       <c r="B7" t="s">
@@ -554,7 +572,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="8">
+      <c r="A8" s="7">
         <v>46272</v>
       </c>
       <c r="B8" t="s">
@@ -565,20 +583,56 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="C9" s="4"/>
+      <c r="A9" s="7">
+        <v>46273</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
+      <c r="A10" s="7">
+        <v>46276</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
+      <c r="A11" s="7">
+        <v>46277</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
+      <c r="A12" s="7">
+        <v>46279</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
+      <c r="A13" s="7">
+        <v>46279</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>

--- a/AT/Research Hours (F26).xlsx
+++ b/AT/Research Hours (F26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abigailtouma/Desktop/SSS-Experiments/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE884E55-4899-3448-AAC2-F0E3A6B644F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D379CC62-2D1D-AB48-8C6E-1D27070A5F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="720" windowWidth="27640" windowHeight="16940" xr2:uid="{9D7B63EE-5957-9947-A3B5-024424A2FDD1}"/>
   </bookViews>
@@ -512,7 +512,7 @@
       </c>
       <c r="E2" s="3">
         <f>SUM(C2:C48)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -632,6 +632,9 @@
       </c>
       <c r="B13" t="s">
         <v>6</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">

--- a/AT/Research Hours (F26).xlsx
+++ b/AT/Research Hours (F26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abigailtouma/Desktop/SSS-Experiments/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D379CC62-2D1D-AB48-8C6E-1D27070A5F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F79C4FE-7E97-C045-A706-AE7273CFB301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="720" windowWidth="27640" windowHeight="16940" xr2:uid="{9D7B63EE-5957-9947-A3B5-024424A2FDD1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -78,6 +78,15 @@
   </si>
   <si>
     <t>continued to look at journals + worked on a few more examples</t>
+  </si>
+  <si>
+    <t>worked on finite examples of new method</t>
+  </si>
+  <si>
+    <t>*catch up for last week</t>
+  </si>
+  <si>
+    <t>continued working on finite examples and began journal search</t>
   </si>
 </sst>
 </file>
@@ -512,7 +521,7 @@
       </c>
       <c r="E2" s="3">
         <f>SUM(C2:C48)</f>
-        <v>12</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -638,41 +647,73 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
+      <c r="A14" s="7">
+        <v>46285</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
+      <c r="A15" s="7">
+        <v>46286</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
+      <c r="A16" s="7">
+        <v>46286</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
+      <c r="A17" s="7">
+        <v>46286</v>
+      </c>
+      <c r="C17">
+        <v>1.5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
+      <c r="A18" s="7"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
+      <c r="A19" s="7"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
+      <c r="A20" s="7"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
+      <c r="A21" s="7"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
+      <c r="A22" s="7"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
+      <c r="A23" s="7"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
+      <c r="A24" s="7"/>
       <c r="C24" s="5"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
+      <c r="A25" s="7"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>

--- a/AT/Research Hours (F26).xlsx
+++ b/AT/Research Hours (F26).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abigailtouma/Desktop/SSS-Experiments/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F79C4FE-7E97-C045-A706-AE7273CFB301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32B25AF1-1753-8B4D-8E42-9A37BD2271AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="720" windowWidth="27640" windowHeight="16940" xr2:uid="{9D7B63EE-5957-9947-A3B5-024424A2FDD1}"/>
+    <workbookView xWindow="1380" yWindow="700" windowWidth="27640" windowHeight="16940" xr2:uid="{9D7B63EE-5957-9947-A3B5-024424A2FDD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hours + Notes" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>Date</t>
   </si>
@@ -83,10 +83,16 @@
     <t>worked on finite examples of new method</t>
   </si>
   <si>
-    <t>*catch up for last week</t>
-  </si>
-  <si>
     <t>continued working on finite examples and began journal search</t>
+  </si>
+  <si>
+    <t>worked on summation notation examples</t>
+  </si>
+  <si>
+    <t>attempted some more examples, journal search</t>
+  </si>
+  <si>
+    <t>journal search, worked through examples in Winzenread journal</t>
   </si>
 </sst>
 </file>
@@ -97,7 +103,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -119,13 +125,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -137,10 +168,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -152,8 +186,25 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="3" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
+    <cellStyle name="20% - Accent4" xfId="2" builtinId="42"/>
+    <cellStyle name="20% - Accent5" xfId="3" builtinId="46"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -486,12 +537,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7542DF9F-5D83-964C-81A0-40C880F500E5}">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="58.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -510,217 +561,242 @@
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="7">
+      <c r="A2" s="9">
         <v>46258</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="13">
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <f>SUM(C2:C48)</f>
-        <v>17.5</v>
+        <f>SUM(C2:C25)</f>
+        <v>19.5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="7">
+      <c r="A3" s="9">
         <v>46265</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="16">
         <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="7">
+      <c r="A4" s="10">
         <v>46265</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="12">
         <v>1</v>
       </c>
       <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="7">
+      <c r="A5" s="10">
         <v>46268</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="12">
         <v>1.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="7">
+      <c r="A6" s="10">
         <v>46269</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="7">
+      <c r="A7" s="10">
         <v>46271</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="12">
         <v>0.75</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="7">
+      <c r="A8" s="11">
         <v>46272</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="14">
         <v>0.75</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="7">
+      <c r="A9" s="11">
         <v>46273</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="7">
+      <c r="A10" s="11">
         <v>46276</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="7">
+      <c r="A11" s="11">
         <v>46277</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="14">
         <v>1.5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="7">
+      <c r="A12" s="11">
         <v>46279</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="7">
+      <c r="A13" s="9">
         <v>46279</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="7">
+      <c r="A14" s="9">
         <v>46285</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="7">
+      <c r="A15" s="9">
         <v>46286</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15">
+        <v>15</v>
+      </c>
+      <c r="C15" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="7">
+      <c r="A16" s="10">
         <v>46286</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="7">
-        <v>46286</v>
-      </c>
-      <c r="C17">
-        <v>1.5</v>
-      </c>
-      <c r="D17" t="s">
-        <v>15</v>
+      <c r="A17" s="10">
+        <v>46291</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="12">
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
+      <c r="A18" s="10">
+        <v>46292</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="12">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
+      <c r="A19" s="10">
+        <v>46295</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="12">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="7"/>
+      <c r="A20" s="10">
+        <v>46295</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="12">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
+      <c r="C21" s="5"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
+      <c r="A23" s="2"/>
+      <c r="C23" s="4"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="7"/>
-      <c r="C24" s="5"/>
+      <c r="A24" s="2"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="7"/>
+      <c r="A25" s="2"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
-      <c r="C26" s="4"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
+      <c r="E27" s="6"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
@@ -730,7 +806,6 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
-      <c r="E30" s="6"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
@@ -776,15 +851,6 @@
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" s="2"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" s="2"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AT/Research Hours (F26).xlsx
+++ b/AT/Research Hours (F26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abigailtouma/Desktop/SSS-Experiments/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32B25AF1-1753-8B4D-8E42-9A37BD2271AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D77A91C5-00F8-AF4B-AEE0-899B42105F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="700" windowWidth="27640" windowHeight="16940" xr2:uid="{9D7B63EE-5957-9947-A3B5-024424A2FDD1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -93,15 +93,17 @@
   </si>
   <si>
     <t>journal search, worked through examples in Winzenread journal</t>
+  </si>
+  <si>
+    <t>continued converting journal examples to I-Cat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -174,17 +176,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -195,11 +193,6 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="3" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
@@ -561,225 +554,240 @@
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="9">
+      <c r="A2" s="7">
         <v>46258</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2">
         <v>1</v>
       </c>
       <c r="E2" s="3">
         <f>SUM(C2:C25)</f>
-        <v>19.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="9">
+      <c r="A3" s="7">
         <v>46265</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3">
         <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="10">
+      <c r="A4" s="8">
         <v>46265</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="12">
-        <v>1</v>
-      </c>
-      <c r="E4" s="8"/>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="10">
+      <c r="A5" s="8">
         <v>46268</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5">
         <v>1.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="10">
+      <c r="A6" s="8">
         <v>46269</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="10">
+      <c r="A7" s="8">
         <v>46271</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7">
         <v>0.75</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="11">
+      <c r="A8" s="9">
         <v>46272</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8">
         <v>0.75</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="11">
+      <c r="A9" s="9">
         <v>46273</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="11">
+      <c r="A10" s="9">
         <v>46276</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="11">
+      <c r="A11" s="9">
         <v>46277</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11">
         <v>1.5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="11">
+      <c r="A12" s="9">
         <v>46279</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="9">
+      <c r="A13" s="7">
         <v>46279</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="9">
+      <c r="A14" s="7">
         <v>46285</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="9">
+      <c r="A15" s="7">
         <v>46286</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="10">
+      <c r="A16" s="8">
         <v>46286</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="10">
+      <c r="A17" s="8">
         <v>46291</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17">
         <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="10">
+      <c r="A18" s="8">
         <v>46292</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="10">
+      <c r="A19" s="8">
         <v>46295</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="10">
+      <c r="A20" s="8">
         <v>46295</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="7"/>
-      <c r="C21" s="5"/>
+      <c r="A21" s="9">
+        <v>46301</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="7"/>
+      <c r="A22" s="9">
+        <v>46302</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
@@ -796,7 +804,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
-      <c r="E27" s="6"/>
+      <c r="E27" s="5"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>

--- a/AT/Research Hours (F26).xlsx
+++ b/AT/Research Hours (F26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abigailtouma/Desktop/SSS-Experiments/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D77A91C5-00F8-AF4B-AEE0-899B42105F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52895EB5-F03E-984B-86E8-D4D4DC69DC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="700" windowWidth="27640" windowHeight="16940" xr2:uid="{9D7B63EE-5957-9947-A3B5-024424A2FDD1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -96,15 +96,18 @@
   </si>
   <si>
     <t>continued converting journal examples to I-Cat</t>
+  </si>
+  <si>
+    <t>worked on I-Cat x I-Cat example and notation</t>
+  </si>
+  <si>
+    <t>journal search + worked on more examples</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -176,13 +179,15 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -193,6 +198,8 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
@@ -530,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7542DF9F-5D83-964C-81A0-40C880F500E5}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="58.5" bestFit="1" customWidth="1"/>
@@ -564,8 +571,8 @@
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <f>SUM(C2:C25)</f>
-        <v>21</v>
+        <f>SUM(C2:C32)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -790,21 +797,41 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="C23" s="4"/>
+      <c r="A23" s="9">
+        <v>46306</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
+      <c r="A24" s="7">
+        <v>46307</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
+      <c r="A25" s="7">
+        <v>46307</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
+      <c r="A26" s="5"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="2"/>
-      <c r="E27" s="5"/>
+      <c r="A27" s="10"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
@@ -853,12 +880,6 @@
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" s="2"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AT/Research Hours (F26).xlsx
+++ b/AT/Research Hours (F26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abigailtouma/Desktop/SSS-Experiments/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52895EB5-F03E-984B-86E8-D4D4DC69DC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3288DD-FA46-F54F-BBCC-AB25EB53C3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="700" windowWidth="27640" windowHeight="16940" xr2:uid="{9D7B63EE-5957-9947-A3B5-024424A2FDD1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>Date</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>journal search + worked on more examples</t>
+  </si>
+  <si>
+    <t>planned for week</t>
   </si>
 </sst>
 </file>
@@ -179,15 +182,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -561,7 +561,7 @@
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>46258</v>
       </c>
       <c r="B2" t="s">
@@ -572,11 +572,11 @@
       </c>
       <c r="E2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>23</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>46265</v>
       </c>
       <c r="B3" t="s">
@@ -587,7 +587,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
+      <c r="A4" s="7">
         <v>46265</v>
       </c>
       <c r="B4" t="s">
@@ -596,10 +596,10 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
+      <c r="A5" s="7">
         <v>46268</v>
       </c>
       <c r="B5" t="s">
@@ -610,7 +610,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="8">
+      <c r="A6" s="7">
         <v>46269</v>
       </c>
       <c r="B6" t="s">
@@ -621,7 +621,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="8">
+      <c r="A7" s="7">
         <v>46271</v>
       </c>
       <c r="B7" t="s">
@@ -632,7 +632,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>46272</v>
       </c>
       <c r="B8" t="s">
@@ -643,7 +643,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>46273</v>
       </c>
       <c r="B9" t="s">
@@ -654,7 +654,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>46276</v>
       </c>
       <c r="B10" t="s">
@@ -665,7 +665,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>46277</v>
       </c>
       <c r="B11" t="s">
@@ -676,7 +676,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>46279</v>
       </c>
       <c r="B12" t="s">
@@ -687,7 +687,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <v>46279</v>
       </c>
       <c r="B13" t="s">
@@ -698,7 +698,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="7">
+      <c r="A14" s="6">
         <v>46285</v>
       </c>
       <c r="B14" t="s">
@@ -709,7 +709,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="7">
+      <c r="A15" s="6">
         <v>46286</v>
       </c>
       <c r="B15" t="s">
@@ -720,7 +720,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="8">
+      <c r="A16" s="7">
         <v>46286</v>
       </c>
       <c r="B16" t="s">
@@ -731,7 +731,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="8">
+      <c r="A17" s="7">
         <v>46291</v>
       </c>
       <c r="B17" t="s">
@@ -742,7 +742,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="8">
+      <c r="A18" s="7">
         <v>46292</v>
       </c>
       <c r="B18" t="s">
@@ -753,7 +753,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="8">
+      <c r="A19" s="7">
         <v>46295</v>
       </c>
       <c r="B19" t="s">
@@ -764,7 +764,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="8">
+      <c r="A20" s="7">
         <v>46295</v>
       </c>
       <c r="B20" t="s">
@@ -775,7 +775,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="9">
+      <c r="A21" s="8">
         <v>46301</v>
       </c>
       <c r="B21" t="s">
@@ -786,7 +786,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="9">
+      <c r="A22" s="8">
         <v>46302</v>
       </c>
       <c r="B22" t="s">
@@ -797,18 +797,18 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="9">
+      <c r="A23" s="8">
         <v>46306</v>
       </c>
       <c r="B23" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="7">
+      <c r="A24" s="6">
         <v>46307</v>
       </c>
       <c r="B24" t="s">
@@ -819,19 +819,30 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="7">
+      <c r="A25" s="6">
         <v>46307</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
       </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
       <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="5"/>
+      <c r="A26" s="6">
+        <v>46307</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="10"/>
+      <c r="A27" s="9"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>

--- a/AT/Research Hours (F26).xlsx
+++ b/AT/Research Hours (F26).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abigailtouma/Desktop/SSS-Experiments/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3288DD-FA46-F54F-BBCC-AB25EB53C3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDD31DCB-80A3-864F-84A5-9071FD0A6D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="700" windowWidth="27640" windowHeight="16940" xr2:uid="{9D7B63EE-5957-9947-A3B5-024424A2FDD1}"/>
+    <workbookView xWindow="1360" yWindow="700" windowWidth="27640" windowHeight="16940" xr2:uid="{9D7B63EE-5957-9947-A3B5-024424A2FDD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hours + Notes" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>Date</t>
   </si>
@@ -105,6 +105,21 @@
   </si>
   <si>
     <t>planned for week</t>
+  </si>
+  <si>
+    <t>went over I-Cat x I-Cat and summation notation (mathematica not working)</t>
+  </si>
+  <si>
+    <t>more summation notation, some finite I-Cat x I-Cat examples</t>
+  </si>
+  <si>
+    <t>looked for I-Cat x I-Cat patterns using Winzenread example</t>
+  </si>
+  <si>
+    <t>more brainstorming; started working through examples on mathematica</t>
+  </si>
+  <si>
+    <t>planned for week; worked through more examples and tested ideas</t>
   </si>
 </sst>
 </file>
@@ -141,7 +156,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,6 +181,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -176,11 +197,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -198,10 +220,13 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="3" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
+    <cellStyle name="20% - Accent1" xfId="4" builtinId="30"/>
     <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
     <cellStyle name="20% - Accent4" xfId="2" builtinId="42"/>
     <cellStyle name="20% - Accent5" xfId="3" builtinId="46"/>
@@ -540,7 +565,7 @@
   <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="58.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
     <col min="7" max="7" width="32" bestFit="1" customWidth="1"/>
   </cols>
@@ -571,8 +596,8 @@
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <f>SUM(C2:C32)</f>
-        <v>24.25</v>
+        <f>SUM(C2:C45)</f>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -803,7 +828,7 @@
       <c r="B23" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <v>1</v>
       </c>
     </row>
@@ -842,25 +867,70 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="9"/>
+      <c r="A27" s="6">
+        <v>46310</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
+      <c r="A28" s="6">
+        <v>46311</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
+      <c r="A29" s="6">
+        <v>46313</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
+      <c r="A30" s="6">
+        <v>46315</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
+      <c r="A31" s="6">
+        <v>46315</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
+      <c r="A32" s="10">
+        <v>46315</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
